--- a/data/vendor-search/results_all_babymonitor.xlsx
+++ b/data/vendor-search/results_all_babymonitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>7.5</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -481,6 +488,11 @@
           <t>cpe:2.3:h:d-link:dcs-900_internet_camera:2.10:*:*:*:*:*:*:*|cpe:2.3:h:d-link:dcs-900_internet_camera:2.20:*:*:*:*:*:*:*|cpe:2.3:h:d-link:dcs-900_internet_camera:2.28:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,8 +513,10 @@
       <c r="D3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E3" t="n">
-        <v>3.1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -512,6 +526,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-2230l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2230l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2310l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2310l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2332l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2332l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-6010l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-6010l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-7010l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7010l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2530l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2530l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-930l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-930l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-932l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-934l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-934l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-942l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-942l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-933l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-933l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5009l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5009l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5010l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5010l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5020l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5020l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5000l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5000l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5025l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5025l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5030l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5030l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2210l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2210l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2136l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2136l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2132l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2132l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-7000l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7000l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-6212l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-6212l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5029l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5029l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2330l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2330l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5222l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5222l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -534,8 +553,10 @@
       <c r="D4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,6 +566,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-5009_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5009:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5010_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5010:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5020l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5020l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -567,8 +593,10 @@
       <c r="D5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -578,6 +606,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -600,8 +633,10 @@
       <c r="D6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -611,6 +646,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -633,8 +673,10 @@
       <c r="D7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -644,6 +686,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -666,8 +713,10 @@
       <c r="D8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -677,6 +726,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -699,8 +753,10 @@
       <c r="D9" t="n">
         <v>7.5</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,6 +766,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -732,8 +793,10 @@
       <c r="D10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,6 +806,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -765,8 +833,10 @@
       <c r="D11" t="n">
         <v>7.5</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -776,6 +846,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -798,8 +873,10 @@
       <c r="D12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -809,6 +886,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -831,8 +913,10 @@
       <c r="D13" t="n">
         <v>7.8</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -842,6 +926,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -864,8 +953,10 @@
       <c r="D14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -875,6 +966,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -897,8 +993,10 @@
       <c r="D15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -908,6 +1006,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -930,8 +1033,10 @@
       <c r="D16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -941,6 +1046,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -963,8 +1073,10 @@
       <c r="D17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -974,6 +1086,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -996,8 +1113,10 @@
       <c r="D18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,6 +1126,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-1100_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1029,8 +1153,10 @@
       <c r="D19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1040,6 +1166,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-935l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-935l:ax:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-960l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-960l:a:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1062,8 +1193,10 @@
       <c r="D20" t="n">
         <v>7.5</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1073,6 +1206,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-3411_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-3411:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-3430_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-3430:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5605_firmware:1.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5605:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5635_firmware:1.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5635:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100l_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130l_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:1.03:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1100_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1100:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:1.03:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-1130_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-1130:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2102_firmware:1.05:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2102_firmware:1.06:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2102:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2121_firmware:1.05:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2121_firmware:1.06:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2121:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-3410_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-3410:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5230_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5230:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5230l_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5230l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-6410_firmware:1.00:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-6410:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-7410_firmware:1.00:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7410:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-7510_firmware:1.00:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7510:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:wcs-1100_firmware:1.00:*:*:*:*:*:*:*|cpe:2.3:h:dlink:wcs-1100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1095,8 +1233,10 @@
       <c r="D21" t="n">
         <v>8</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1104,6 +1244,11 @@
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5000l_firmware:1.05:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5000l:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1124,8 +1269,10 @@
       <c r="D22" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E22" t="n">
-        <v>3.1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1135,6 +1282,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-960l_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-960l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1157,8 +1309,10 @@
       <c r="D23" t="n">
         <v>7.5</v>
       </c>
-      <c r="E23" t="n">
-        <v>3.1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1166,6 +1320,11 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>hubble connected</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1186,8 +1345,10 @@
       <c r="D24" t="n">
         <v>9</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1197,6 +1358,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>cpe:2.3:a:dlink:dcs-2121_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2121:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1219,8 +1385,10 @@
       <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1230,6 +1398,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:a:dlink:dcs-2121_firmware:1.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2121:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1252,8 +1425,10 @@
       <c r="D26" t="n">
         <v>3.3</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1263,6 +1438,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:1.02:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1285,8 +1465,10 @@
       <c r="D27" t="n">
         <v>6.8</v>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1296,6 +1478,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1318,8 +1505,10 @@
       <c r="D28" t="n">
         <v>9</v>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -1327,6 +1516,11 @@
           <t>cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1347,8 +1541,10 @@
       <c r="D29" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E29" t="n">
-        <v>3</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1358,6 +1554,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:o:d-link:dcs-936l:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-936l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1380,8 +1581,10 @@
       <c r="D30" t="n">
         <v>5.3</v>
       </c>
-      <c r="E30" t="n">
-        <v>3</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,6 +1594,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cpe:2.3:a:babyphonemobile:wifi_baby_monitor:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>wifi baby monitor|baby monitor</t>
         </is>
       </c>
     </row>
@@ -1413,8 +1621,10 @@
       <c r="D31" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E31" t="n">
-        <v>3</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1424,6 +1634,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:eyeon_baby_monitor_firmware:1.08.1:*:*:*:*:*:*:*|cpe:2.3:h:dlink:eyeon_baby_monitor:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>baby monitor</t>
         </is>
       </c>
     </row>
@@ -1446,8 +1661,10 @@
       <c r="D32" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E32" t="n">
-        <v>3</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1457,6 +1674,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:eyeon_baby_monitor_firmware:1.08.1:*:*:*:*:*:*:*|cpe:2.3:h:dlink:eyeon_baby_monitor:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>baby monitor</t>
         </is>
       </c>
     </row>
@@ -1479,8 +1701,10 @@
       <c r="D33" t="n">
         <v>7.5</v>
       </c>
-      <c r="E33" t="n">
-        <v>3</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1490,6 +1714,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>cpe:2.3:o:d-link:dcs-936l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-936l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-942l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-942l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-8000lh_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8000lh:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-942lb1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-942lb1:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-5222l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5222l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-825l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-825l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-2630l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2630l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-820l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-820l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-855l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-855l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-2121_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2121:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-5222lb1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5222lb1:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5020l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5020l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-930l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-930l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-8100lh_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8100lh:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-932l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*|cpe:2.3:o:d-link:dcs-2102_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2102:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-933l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-933l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5030l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5030l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1512,8 +1741,10 @@
       <c r="D34" t="n">
         <v>7.5</v>
       </c>
-      <c r="E34" t="n">
-        <v>3</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -1521,6 +1752,11 @@
           <t>cpe:2.3:o:d-link:dcs-825l_firmware:1.08:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-825l:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1541,8 +1777,10 @@
       <c r="D35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E35" t="n">
-        <v>3</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1552,6 +1790,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-930l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-930l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-932l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-933l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-933l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-934l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-934l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5009l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5009l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5010l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5010l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5020l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5020l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5025l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5025l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-5030l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5030l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1574,8 +1817,10 @@
       <c r="D36" t="n">
         <v>7.2</v>
       </c>
-      <c r="E36" t="n">
-        <v>3.1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1585,6 +1830,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-930l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-930l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1607,8 +1857,10 @@
       <c r="D37" t="n">
         <v>7.5</v>
       </c>
-      <c r="E37" t="n">
-        <v>3.1</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -1616,6 +1868,11 @@
           <t>cpe:2.3:o:dlink:dcs-4603_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4603:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4622_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4622:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4701e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4701e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4703e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4703e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4705e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4705e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4802e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4802e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-p703_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-p703:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2530l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2530l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2670l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2670l:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1636,8 +1893,10 @@
       <c r="D38" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E38" t="n">
-        <v>3.1</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1647,6 +1906,11 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-4703e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4703e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4705e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4705e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4802e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4802e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-p703_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-p703:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4603_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4603:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4622_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4622:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-4701e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-4701e:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2530l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2530l:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-2670l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-2670l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1669,8 +1933,10 @@
       <c r="D39" t="n">
         <v>8</v>
       </c>
-      <c r="E39" t="n">
-        <v>3.1</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1680,6 +1946,11 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-5220_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5220:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1703,8 +1974,10 @@
       <c r="D40" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.1</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1714,6 +1987,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1737,8 +2015,10 @@
       <c r="D41" t="n">
         <v>8</v>
       </c>
-      <c r="E41" t="n">
-        <v>3.1</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1748,6 +2028,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1771,8 +2056,10 @@
       <c r="D42" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E42" t="n">
-        <v>3.1</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1782,6 +2069,11 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1805,8 +2097,10 @@
       <c r="D43" t="n">
         <v>8</v>
       </c>
-      <c r="E43" t="n">
-        <v>3.1</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1816,6 +2110,11 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1839,8 +2138,10 @@
       <c r="D44" t="n">
         <v>8</v>
       </c>
-      <c r="E44" t="n">
-        <v>3.1</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1850,6 +2151,11 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1873,8 +2179,10 @@
       <c r="D45" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E45" t="n">
-        <v>3.1</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1884,6 +2192,11 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-8300lhv2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-8300lhv2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1906,8 +2219,10 @@
       <c r="D46" t="n">
         <v>6.5</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1915,6 +2230,11 @@
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>baby monitor</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1935,8 +2255,10 @@
       <c r="D47" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E47" t="n">
-        <v>3.1</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1946,6 +2268,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-960l_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-960l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -1968,8 +2295,10 @@
       <c r="D48" t="n">
         <v>6.5</v>
       </c>
-      <c r="E48" t="n">
-        <v>3.1</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1979,6 +2308,11 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2001,8 +2335,10 @@
       <c r="D49" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E49" t="n">
-        <v>3.1</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2012,6 +2348,11 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2034,8 +2375,10 @@
       <c r="D50" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E50" t="n">
-        <v>3.1</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2045,6 +2388,11 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2067,8 +2415,10 @@
       <c r="D51" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E51" t="n">
-        <v>3.1</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2078,6 +2428,11 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2100,8 +2455,10 @@
       <c r="D52" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E52" t="n">
-        <v>3.1</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2111,6 +2468,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-5020l_firmware:1.01_b2:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5020l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2133,8 +2495,10 @@
       <c r="D53" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E53" t="n">
-        <v>3.1</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2144,6 +2508,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2166,8 +2535,10 @@
       <c r="D54" t="n">
         <v>7.5</v>
       </c>
-      <c r="E54" t="n">
-        <v>3.1</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2177,6 +2548,11 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2199,8 +2575,10 @@
       <c r="D55" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E55" t="n">
-        <v>3.1</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2210,6 +2588,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2232,8 +2615,10 @@
       <c r="D56" t="n">
         <v>5.4</v>
       </c>
-      <c r="E56" t="n">
-        <v>3.1</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2243,6 +2628,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-6010l_firmware:1.15.03:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-6010l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2265,8 +2655,10 @@
       <c r="D57" t="n">
         <v>7.4</v>
       </c>
-      <c r="E57" t="n">
-        <v>3.1</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2276,6 +2668,11 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-6517_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-6517:-:*:*:*:*:*:*:*|cpe:2.3:o:dlink:dcs-7517_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7517:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2298,8 +2695,10 @@
       <c r="D58" t="n">
         <v>3.7</v>
       </c>
-      <c r="E58" t="n">
-        <v>3.1</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2309,6 +2708,11 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-7517_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-7517:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2331,8 +2735,10 @@
       <c r="D59" t="n">
         <v>7.3</v>
       </c>
-      <c r="E59" t="n">
-        <v>3.1</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2342,6 +2748,11 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-825l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-825l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2364,8 +2775,10 @@
       <c r="D60" t="n">
         <v>6.6</v>
       </c>
-      <c r="E60" t="n">
-        <v>3.1</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2375,6 +2788,11 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-825l_firmware:1.08.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-825l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2397,8 +2815,10 @@
       <c r="D61" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E61" t="n">
-        <v>3.1</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2408,6 +2828,11 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-935l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-935l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2430,8 +2855,10 @@
       <c r="D62" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E62" t="n">
-        <v>3.1</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2441,6 +2868,11 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-930l_firmware:1.15.04:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-930l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2463,8 +2895,10 @@
       <c r="D63" t="n">
         <v>3.3</v>
       </c>
-      <c r="E63" t="n">
-        <v>3.1</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2474,6 +2908,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-850l_firmware:1.02.09:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-850l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2496,8 +2935,10 @@
       <c r="D64" t="n">
         <v>5.5</v>
       </c>
-      <c r="E64" t="n">
-        <v>3.1</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2507,6 +2948,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-700l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-700l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2529,8 +2975,10 @@
       <c r="D65" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E65" t="n">
-        <v>3.1</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2540,6 +2988,11 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-933l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-933l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2562,8 +3015,10 @@
       <c r="D66" t="n">
         <v>7.2</v>
       </c>
-      <c r="E66" t="n">
-        <v>3.1</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2573,6 +3028,11 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2595,8 +3055,10 @@
       <c r="D67" t="n">
         <v>7.2</v>
       </c>
-      <c r="E67" t="n">
-        <v>3.1</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2606,6 +3068,11 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-931l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-931l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2628,8 +3095,10 @@
       <c r="D68" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E68" t="n">
-        <v>3.1</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2639,6 +3108,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-935l_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-935l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2661,8 +3135,10 @@
       <c r="D69" t="n">
         <v>7.5</v>
       </c>
-      <c r="E69" t="n">
-        <v>3.1</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2670,6 +3146,11 @@
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>baby monitor</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2690,8 +3171,10 @@
       <c r="D70" t="n">
         <v>7.3</v>
       </c>
-      <c r="E70" t="n">
-        <v>3.1</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2701,6 +3184,11 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-932l_firmware:2.18.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-932l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2723,8 +3211,10 @@
       <c r="D71" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E71" t="n">
-        <v>3.1</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2734,6 +3224,11 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-5615_firmware:1.01.00:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5615:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2756,8 +3251,10 @@
       <c r="D72" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E72" t="n">
-        <v>3.1</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2767,6 +3264,11 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dlink:dcs-935l_firmware:1.10.01:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-935l:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2789,8 +3291,10 @@
       <c r="D73" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E73" t="n">
-        <v>2</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2800,6 +3304,11 @@
       <c r="G73" t="inlineStr">
         <is>
           <t>cpe:2.3:a:dlink:camera_stream_client_activex_control:1.0.0.4519:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5605_ptz_ip_network_camera:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
@@ -2822,8 +3331,10 @@
       <c r="D74" t="n">
         <v>6.8</v>
       </c>
-      <c r="E74" t="n">
-        <v>2</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2833,6 +3344,11 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>cpe:2.3:h:dlink:dcs-2000:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-5300:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dcs-900:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>d-link dcs</t>
         </is>
       </c>
     </row>
